--- a/data/trans_camb/IP22_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP22_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 20,11</t>
+          <t>-8,24; 18,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 26,36</t>
+          <t>-0,69; 25,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 27,89</t>
+          <t>-5,0; 28,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 31,62</t>
+          <t>1,29; 30,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 16,51</t>
+          <t>-10,48; 17,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 9,48</t>
+          <t>-16,28; 8,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 21,06</t>
+          <t>1,36; 20,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 18,33</t>
+          <t>-2,33; 18,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 14,21</t>
+          <t>-7,96; 12,72</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 112,03</t>
+          <t>-25,67; 100,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 152,07</t>
+          <t>-4,04; 137,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 156,41</t>
+          <t>-20,24; 151,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 144,9</t>
+          <t>3,25; 134,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 70,94</t>
+          <t>-28,79; 84,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,49; 45,69</t>
+          <t>-48,04; 37,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 96,81</t>
+          <t>3,49; 96,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 79,24</t>
+          <t>-7,5; 81,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 60,02</t>
+          <t>-25,08; 55,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 20,38</t>
+          <t>2,89; 20,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 17,13</t>
+          <t>-1,79; 16,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 2,98</t>
+          <t>-18,8; 1,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 20,87</t>
+          <t>1,69; 22,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 11,29</t>
+          <t>-7,85; 11,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -3,36</t>
+          <t>-20,76; -3,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 17,6</t>
+          <t>4,97; 18,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 11,03</t>
+          <t>-1,93; 11,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,17; -3,76</t>
+          <t>-16,17; -3,6</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 129,94</t>
+          <t>9,93; 136,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 110,04</t>
+          <t>-7,5; 101,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-69,08; 15,94</t>
+          <t>-76,38; 6,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 106,64</t>
+          <t>6,06; 114,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 55,96</t>
+          <t>-27,86; 55,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,88; -14,39</t>
+          <t>-71,51; -18,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,43; 93,08</t>
+          <t>18,84; 102,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 57,87</t>
+          <t>-8,91; 58,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,02; -19,37</t>
+          <t>-63,25; -16,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 20,67</t>
+          <t>-3,79; 21,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,58; -3,35</t>
+          <t>-23,63; -4,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 12,16</t>
+          <t>-11,8; 12,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 20,7</t>
+          <t>-3,74; 20,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,44; -10,57</t>
+          <t>-28,02; -10,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 0,04</t>
+          <t>-20,53; -0,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 17,64</t>
+          <t>0,06; 17,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,95; -9,44</t>
+          <t>-22,5; -8,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 1,84</t>
+          <t>-12,53; 3,23</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 127,38</t>
+          <t>-13,52; 134,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,75; -16,41</t>
+          <t>-82,05; -18,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,73; 77,13</t>
+          <t>-42,85; 77,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 120,43</t>
+          <t>-14,48; 111,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-94,91; -46,11</t>
+          <t>-95,94; -52,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,55; 3,5</t>
+          <t>-72,51; -0,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 95,53</t>
+          <t>0,95; 91,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,67; -48,11</t>
+          <t>-84,03; -43,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,01; 11,09</t>
+          <t>-47,63; 17,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 14,63</t>
+          <t>-6,95; 16,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 14,82</t>
+          <t>-6,92; 15,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 8,08</t>
+          <t>-15,49; 6,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 19,14</t>
+          <t>-4,72; 19,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 23,22</t>
+          <t>1,04; 25,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 9,52</t>
+          <t>-17,3; 9,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 14,26</t>
+          <t>-2,03; 13,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 16,27</t>
+          <t>0,17; 16,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 5,46</t>
+          <t>-12,95; 4,6</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,68; 93,16</t>
+          <t>-27,69; 106,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 102,41</t>
+          <t>-26,39; 103,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,02; 55,05</t>
+          <t>-59,22; 48,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 110,75</t>
+          <t>-17,09; 123,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 138,04</t>
+          <t>3,08; 150,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,23; 54,46</t>
+          <t>-65,23; 54,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 79,87</t>
+          <t>-8,23; 74,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 91,15</t>
+          <t>0,55; 93,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,8; 31,51</t>
+          <t>-53,73; 23,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,02; 37,89</t>
+          <t>9,52; 38,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 7,4</t>
+          <t>-14,19; 8,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-20,84; 0,54</t>
+          <t>-19,77; 1,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 25,22</t>
+          <t>-0,96; 25,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-20,29; -3,38</t>
+          <t>-21,7; -2,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 2,34</t>
+          <t>-17,09; 2,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,88; 28,03</t>
+          <t>7,97; 28,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 0,53</t>
+          <t>-14,87; -0,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-15,32; -1,35</t>
+          <t>-15,68; -1,08</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>37,65; 554,16</t>
+          <t>41,18; 514,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-74,68; 109,51</t>
+          <t>-72,94; 149,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-93,02; 27,84</t>
+          <t>-100,0; 37,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 324,45</t>
+          <t>-7,71; 363,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,43</t>
+          <t>-100,0; 5,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-88,18; 44,84</t>
+          <t>-84,73; 76,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,42; 280,12</t>
+          <t>41,08; 305,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-78,77; 8,14</t>
+          <t>-81,54; -0,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-83,16; -7,67</t>
+          <t>-82,86; 4,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 20,66</t>
+          <t>-6,71; 20,18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 12,12</t>
+          <t>-13,17; 13,01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 3,1</t>
+          <t>-21,82; 1,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 25,86</t>
+          <t>-3,48; 24,33</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 2,81</t>
+          <t>-20,69; 3,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 3,19</t>
+          <t>-20,01; 4,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 18,75</t>
+          <t>0,23; 19,07</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 4,51</t>
+          <t>-12,18; 4,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-17,36; -0,56</t>
+          <t>-16,91; 0,53</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 126,38</t>
+          <t>-22,75; 128,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-48,69; 76,26</t>
+          <t>-44,98; 76,35</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,77; 26,01</t>
+          <t>-73,71; 14,68</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 141,26</t>
+          <t>-10,87; 134,89</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-67,19; 16,87</t>
+          <t>-68,62; 20,42</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-64,01; 22,34</t>
+          <t>-66,19; 27,38</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 100,9</t>
+          <t>0,09; 99,21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-48,07; 24,59</t>
+          <t>-45,79; 26,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-60,49; 1,4</t>
+          <t>-61,84; 5,5</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 9,15</t>
+          <t>-8,72; 9,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-19,61; -4,74</t>
+          <t>-18,91; -4,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 6,53</t>
+          <t>-11,52; 6,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 14,57</t>
+          <t>-2,29; 14,94</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-22,11; -8,06</t>
+          <t>-22,06; -8,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 10,86</t>
+          <t>-7,23; 11,58</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 9,41</t>
+          <t>-3,11; 8,96</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-18,85; -9,02</t>
+          <t>-18,93; -8,49</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 6,92</t>
+          <t>-6,48; 6,84</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 52,91</t>
+          <t>-32,47; 47,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-70,22; -22,45</t>
+          <t>-70,32; -23,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 38,14</t>
+          <t>-43,54; 33,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 78,65</t>
+          <t>-7,92; 80,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-80,77; -42,53</t>
+          <t>-79,98; -43,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-23,95; 57,54</t>
+          <t>-26,81; 65,39</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 45,67</t>
+          <t>-12,11; 44,74</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-71,96; -42,59</t>
+          <t>-72,23; -42,99</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 34,61</t>
+          <t>-24,86; 34,49</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 0,19</t>
+          <t>-10,98; -0,05</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 2,58</t>
+          <t>-8,13; 2,57</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -5,1</t>
+          <t>-14,87; -5,22</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-14,22; -2,68</t>
+          <t>-13,31; -1,86</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 2,46</t>
+          <t>-9,77; 2,61</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,15; -5,65</t>
+          <t>-17,26; -6,46</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,71; -2,89</t>
+          <t>-10,41; -2,94</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 1,05</t>
+          <t>-6,64; 1,76</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-14,53; -7,28</t>
+          <t>-14,31; -7,02</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 5,63</t>
+          <t>-66,72; 3,06</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 28,46</t>
+          <t>-51,26; 27,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-91,31; -49,19</t>
+          <t>-90,1; -42,73</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-68,87; -16,38</t>
+          <t>-67,95; -11,23</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 19,26</t>
+          <t>-49,08; 21,38</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-86,12; -37,31</t>
+          <t>-85,94; -44,04</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-62,59; -22,53</t>
+          <t>-62,6; -21,97</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-40,27; 8,86</t>
+          <t>-41,3; 13,78</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-84,65; -56,0</t>
+          <t>-85,41; -55,45</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,8</t>
+          <t>0,53; 7,88</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,81</t>
+          <t>-4,98; 1,57</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,04</t>
+          <t>-7,44; 0,4</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,07; 9,54</t>
+          <t>2,42; 9,52</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-8,44; -1,6</t>
+          <t>-8,24; -2,03</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-9,98; -2,94</t>
+          <t>-10,1; -3,14</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,0</t>
+          <t>2,64; 7,72</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -1,04</t>
+          <t>-5,62; -0,92</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,55; -2,53</t>
+          <t>-7,64; -2,45</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>3,34; 43,94</t>
+          <t>3,03; 45,74</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 10,79</t>
+          <t>-23,77; 9,31</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-36,63; 0,63</t>
+          <t>-36,19; 1,46</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,59; 47,74</t>
+          <t>10,12; 46,98</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-35,27; -8,01</t>
+          <t>-35,32; -10,08</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-42,7; -14,47</t>
+          <t>-42,06; -15,21</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,85; 41,84</t>
+          <t>12,21; 39,42</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-26,34; -5,24</t>
+          <t>-25,87; -4,76</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -12,33</t>
+          <t>-35,75; -12,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP22_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP22_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,84</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-3,17</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,02</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>12,23</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10,14</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15,88</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,54</t>
+          <t>7,69</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>1,9</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 18,18</t>
+          <t>0,72; 29,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 25,49</t>
+          <t>-9,68; 18,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 28,6</t>
+          <t>-15,82; 10,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 30,31</t>
+          <t>-7,4; 18,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 17,71</t>
+          <t>-1,23; 26,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 8,92</t>
+          <t>-6,76; 20,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 20,93</t>
+          <t>1,53; 21,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 18,19</t>
+          <t>-0,82; 18,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 12,72</t>
+          <t>-8,03; 11,56</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>53,74%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-10,74%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>24,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>49,46%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>40,99%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53,74%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-15,36%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,67; 100,72</t>
+          <t>3,17; 138,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 137,52</t>
+          <t>-26,45; 79,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 151,61</t>
+          <t>-45,22; 46,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 134,19</t>
+          <t>-23,69; 109,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,79; 84,29</t>
+          <t>-4,68; 138,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,04; 37,39</t>
+          <t>-21,93; 110,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 96,47</t>
+          <t>5,22; 98,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 81,2</t>
+          <t>-3,88; 82,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 55,77</t>
+          <t>-25,02; 49,15</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,44</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-12,56</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>11,45</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,02</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-6,74</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,65</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,41</t>
+          <t>-2,87</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-9,65</t>
+          <t>-7,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 20,95</t>
+          <t>1,72; 21,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 16,35</t>
+          <t>-7,78; 10,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 1,33</t>
+          <t>-21,22; -3,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 22,78</t>
+          <t>1,33; 21,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 11,06</t>
+          <t>-0,89; 17,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,76; -3,77</t>
+          <t>-11,88; 6,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 18,83</t>
+          <t>4,8; 19,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 11,22</t>
+          <t>-2,07; 11,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,17; -3,6</t>
+          <t>-13,67; -0,65</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47,9%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-51,67%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>57,58%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>40,33%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-33,92%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>47,9%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-51,05%</t>
+          <t>-14,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-43,55%</t>
+          <t>-35,99%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,93; 136,53</t>
+          <t>5,38; 107,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 101,91</t>
+          <t>-27,65; 52,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,38; 6,21</t>
+          <t>-72,86; -13,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,06; 114,71</t>
+          <t>4,65; 129,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 55,69</t>
+          <t>-4,51; 111,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,51; -18,66</t>
+          <t>-51,56; 41,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,84; 102,3</t>
+          <t>19,55; 104,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 58,73</t>
+          <t>-8,18; 58,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-63,25; -16,6</t>
+          <t>-54,25; -3,74</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,85</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-18,84</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-10,6</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>8,67</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-13,46</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,85</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-18,84</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,22</t>
+          <t>-0,88</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-5,88</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 21,35</t>
+          <t>-2,21; 21,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,63; -4,08</t>
+          <t>-28,12; -10,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 12,18</t>
+          <t>-21,12; -0,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 20,2</t>
+          <t>-3,64; 21,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,02; -10,41</t>
+          <t>-24,32; -3,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,53; -0,22</t>
+          <t>-12,91; 10,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 17,01</t>
+          <t>0,36; 17,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,5; -8,71</t>
+          <t>-22,44; -9,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 3,23</t>
+          <t>-12,64; 2,49</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38,05%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-80,98%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-45,55%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>39,13%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-60,76%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-0,11%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>38,05%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-80,98%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-43,94%</t>
+          <t>-3,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-24,14%</t>
+          <t>-25,88%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 134,77</t>
+          <t>-10,26; 119,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,05; -18,09</t>
+          <t>-95,59; -47,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 77,07</t>
+          <t>-71,07; -0,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 111,34</t>
+          <t>-14,72; 130,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-95,94; -52,87</t>
+          <t>-84,85; -14,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,51; -0,22</t>
+          <t>-46,29; 71,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 91,14</t>
+          <t>1,36; 92,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,03; -43,83</t>
+          <t>-85,03; -46,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 17,99</t>
+          <t>-49,77; 13,92</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12,21</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-3,62</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,59</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,75</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,81</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,17</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>12,21</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,21</t>
+          <t>-2,71</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,0</t>
+          <t>-3,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 16,07</t>
+          <t>-4,84; 18,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 15,71</t>
+          <t>0,56; 23,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 6,73</t>
+          <t>-16,05; 11,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 19,22</t>
+          <t>-6,38; 17,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 25,16</t>
+          <t>-6,37; 16,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 9,48</t>
+          <t>-14,48; 9,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 13,49</t>
+          <t>-2,13; 14,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 16,71</t>
+          <t>0,61; 16,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 4,6</t>
+          <t>-12,73; 5,86</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>32,17%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>54,77%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-16,22%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>21,89%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>22,66%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-18,2%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>32,17%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>54,77%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-18,88%</t>
+          <t>-12,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-18,5%</t>
+          <t>-14,69%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 106,01</t>
+          <t>-17,66; 108,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 103,07</t>
+          <t>1,6; 145,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 48,01</t>
+          <t>-62,78; 66,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 123,32</t>
+          <t>-26,12; 124,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,08; 150,48</t>
+          <t>-22,34; 114,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 54,85</t>
+          <t>-56,25; 59,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 74,36</t>
+          <t>-8,48; 86,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 93,18</t>
+          <t>1,29; 89,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,73; 23,26</t>
+          <t>-51,68; 29,39</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12,74</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-11,01</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-6,87</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>22,98</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,39</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-9,22</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>12,74</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-11,01</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-7,0</t>
+          <t>-9,99</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-8,03</t>
+          <t>-8,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9,52; 38,06</t>
+          <t>-0,53; 27,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 8,79</t>
+          <t>-21,65; -3,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 1,11</t>
+          <t>-16,66; 3,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 25,87</t>
+          <t>8,43; 38,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-21,7; -2,49</t>
+          <t>-14,92; 8,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 2,7</t>
+          <t>-20,49; -0,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,97; 28,03</t>
+          <t>8,43; 27,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,87; -0,74</t>
+          <t>-15,01; 0,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-15,68; -1,08</t>
+          <t>-15,78; -2,01</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-80,18%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-50,03%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>161,29%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-23,82%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-64,71%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>92,74%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-80,18%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-50,93%</t>
+          <t>-70,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-57,41%</t>
+          <t>-59,75%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>41,18; 514,02</t>
+          <t>-6,98; 388,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-72,94; 149,2</t>
+          <t>-100,0; -6,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 37,31</t>
+          <t>-84,42; 88,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 363,73</t>
+          <t>29,74; 481,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 5,55</t>
+          <t>-72,74; 105,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-84,73; 76,92</t>
+          <t>-93,63; 25,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,08; 305,44</t>
+          <t>38,71; 300,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-81,54; -0,62</t>
+          <t>-80,33; 6,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,86; 4,61</t>
+          <t>-84,4; -11,2</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>11,29</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-8,7</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-8,89</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>7,42</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-9,15</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>11,29</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-8,7</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-8,33</t>
+          <t>-9,25</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-8,62</t>
+          <t>-9,06</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 20,18</t>
+          <t>-0,97; 26,22</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 13,01</t>
+          <t>-19,94; 3,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 1,85</t>
+          <t>-20,0; 3,56</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 24,33</t>
+          <t>-5,62; 21,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 3,04</t>
+          <t>-12,73; 14,38</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 4,39</t>
+          <t>-21,24; 1,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,23; 19,07</t>
+          <t>-0,31; 19,37</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 4,81</t>
+          <t>-13,16; 4,28</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 0,53</t>
+          <t>-16,73; -0,51</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>46,05%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-35,49%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-36,28%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>33,33%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>0,68%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-41,12%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>46,05%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-35,49%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-33,97%</t>
+          <t>-41,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-36,83%</t>
+          <t>-38,69%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 128,16</t>
+          <t>-4,27; 152,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 76,35</t>
+          <t>-69,31; 21,19</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-73,71; 14,68</t>
+          <t>-66,88; 17,63</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 134,89</t>
+          <t>-23,48; 138,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-68,62; 20,42</t>
+          <t>-44,89; 90,93</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-66,19; 27,38</t>
+          <t>-72,83; 16,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,09; 99,21</t>
+          <t>-1,44; 103,21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-45,79; 26,04</t>
+          <t>-48,51; 20,81</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-61,84; 5,5</t>
+          <t>-61,27; -1,92</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>6,52</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-15,25</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2,79</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-0,08</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-11,98</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-3,11</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>6,52</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-15,25</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>-3,34</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 9,04</t>
+          <t>-2,17; 14,8</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-18,91; -4,65</t>
+          <t>-22,92; -8,87</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 6,15</t>
+          <t>-6,18; 11,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 14,94</t>
+          <t>-8,75; 8,31</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-22,06; -8,33</t>
+          <t>-18,95; -5,4</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 11,58</t>
+          <t>-12,59; 4,73</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 8,96</t>
+          <t>-2,94; 8,96</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -8,49</t>
+          <t>-19,13; -9,32</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 6,84</t>
+          <t>-6,46; 6,21</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>28,28%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-66,19%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-0,35%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-52,5%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-13,63%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>28,28%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-66,19%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>-14,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-0,25%</t>
+          <t>-0,23%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 47,45</t>
+          <t>-9,1; 74,99</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-70,32; -23,86</t>
+          <t>-80,14; -44,11</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-43,54; 33,88</t>
+          <t>-24,24; 59,54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 80,76</t>
+          <t>-31,97; 44,51</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-79,98; -43,88</t>
+          <t>-70,36; -25,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,81; 65,39</t>
+          <t>-44,72; 27,79</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 44,74</t>
+          <t>-11,97; 43,83</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-72,23; -42,99</t>
+          <t>-72,27; -44,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 34,49</t>
+          <t>-25,09; 31,45</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-7,82</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-3,33</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-11,77</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-5,28</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-2,61</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-9,68</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-7,82</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-3,33</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-11,56</t>
+          <t>-9,67</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-10,58</t>
+          <t>-10,7</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-10,98; -0,05</t>
+          <t>-13,82; -2,31</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 2,57</t>
+          <t>-9,3; 2,71</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,87; -5,22</t>
+          <t>-17,48; -6,72</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-13,31; -1,86</t>
+          <t>-10,56; -0,02</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 2,61</t>
+          <t>-8,06; 2,61</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-17,26; -6,46</t>
+          <t>-14,7; -5,28</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -2,94</t>
+          <t>-10,75; -2,74</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,76</t>
+          <t>-7,06; 0,86</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-14,31; -7,02</t>
+          <t>-14,33; -7,16</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-48,02%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-20,41%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-72,25%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-41,67%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-20,6%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-76,39%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-48,02%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-20,41%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-70,93%</t>
+          <t>-76,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-72,86%</t>
+          <t>-73,73%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-66,72; 3,06</t>
+          <t>-69,27; -13,37</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-51,26; 27,42</t>
+          <t>-49,04; 20,27</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-90,1; -42,73</t>
+          <t>-88,66; -47,32</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-67,95; -11,23</t>
+          <t>-68,0; 0,05</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 21,38</t>
+          <t>-52,84; 27,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-85,94; -44,04</t>
+          <t>-89,4; -46,4</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-62,6; -21,97</t>
+          <t>-62,44; -20,68</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 13,78</t>
+          <t>-41,92; 8,92</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-85,41; -55,45</t>
+          <t>-84,6; -57,08</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>5,83</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-4,99</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-6,66</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>4,28</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-1,72</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-3,8</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>5,83</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-4,99</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-6,39</t>
+          <t>-4,08</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-5,14</t>
+          <t>-5,41</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,88</t>
+          <t>2,42; 9,4</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,57</t>
+          <t>-8,45; -1,78</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 0,4</t>
+          <t>-9,87; -2,95</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,52</t>
+          <t>0,78; 7,65</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-8,24; -2,03</t>
+          <t>-5,13; 1,43</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-10,1; -3,14</t>
+          <t>-7,66; -0,89</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,72</t>
+          <t>2,28; 7,67</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,62; -0,92</t>
+          <t>-5,78; -1,06</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,64; -2,45</t>
+          <t>-7,96; -2,84</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>26,85%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-22,97%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-30,64%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>22,13%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-8,88%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-19,66%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-22,97%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-29,43%</t>
+          <t>-21,12%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-24,99%</t>
+          <t>-26,31%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>3,03; 45,74</t>
+          <t>10,04; 46,86</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 9,31</t>
+          <t>-35,6; -8,79</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 1,46</t>
+          <t>-42,17; -14,27</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>10,12; 46,98</t>
+          <t>3,46; 43,03</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-35,32; -10,08</t>
+          <t>-24,9; 7,83</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-42,06; -15,21</t>
+          <t>-35,97; -4,19</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>12,21; 39,42</t>
+          <t>10,12; 39,47</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-25,87; -4,76</t>
+          <t>-26,27; -5,3</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-35,75; -12,64</t>
+          <t>-36,19; -14,46</t>
         </is>
       </c>
     </row>
